--- a/new updates/java_interviews_updated (version 2).xlsx
+++ b/new updates/java_interviews_updated (version 2).xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA6DFAE-A209-4982-90A8-5931BFCE0FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{06F0298F-39CB-45B1-A366-BCCF7240D96A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{06F0298F-39CB-45B1-A366-BCCF7240D96A}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="18" r:id="rId1"/>
@@ -28511,10 +28511,10 @@
     <xf numFmtId="0" fontId="76" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -28871,7 +28871,7 @@
       <c r="B2" s="10">
         <v>117</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="66" t="s">
         <v>1909</v>
       </c>
       <c r="D2" s="30"/>
@@ -28886,12 +28886,12 @@
       <c r="B3" s="10">
         <v>50</v>
       </c>
-      <c r="C3" s="65"/>
+      <c r="C3" s="66"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
       <c r="F3" s="30"/>
       <c r="G3" s="30"/>
-      <c r="H3" s="66" t="s">
+      <c r="H3" s="65" t="s">
         <v>2245</v>
       </c>
     </row>
@@ -28902,7 +28902,7 @@
       <c r="B4" s="10">
         <v>44</v>
       </c>
-      <c r="C4" s="65"/>
+      <c r="C4" s="66"/>
       <c r="D4" s="30"/>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -28918,7 +28918,7 @@
       <c r="B5" s="10">
         <v>69</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="66" t="s">
         <v>1910</v>
       </c>
       <c r="D5" s="30"/>
@@ -28936,7 +28936,7 @@
       <c r="B6" s="10">
         <v>115</v>
       </c>
-      <c r="C6" s="65"/>
+      <c r="C6" s="66"/>
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -28952,7 +28952,7 @@
       <c r="B7" s="10">
         <v>66</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="66" t="s">
         <v>1911</v>
       </c>
       <c r="D7" s="30"/>
@@ -28967,7 +28967,7 @@
       <c r="B8" s="10">
         <v>23</v>
       </c>
-      <c r="C8" s="65"/>
+      <c r="C8" s="66"/>
       <c r="D8" s="30"/>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
@@ -28980,7 +28980,7 @@
       <c r="B9" s="10">
         <v>105</v>
       </c>
-      <c r="C9" s="65"/>
+      <c r="C9" s="66"/>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
@@ -28993,7 +28993,7 @@
       <c r="B10" s="10">
         <v>30</v>
       </c>
-      <c r="C10" s="65" t="s">
+      <c r="C10" s="66" t="s">
         <v>1912</v>
       </c>
       <c r="D10" s="30"/>
@@ -29008,7 +29008,7 @@
       <c r="B11" s="10">
         <v>64</v>
       </c>
-      <c r="C11" s="65"/>
+      <c r="C11" s="66"/>
       <c r="D11" s="30"/>
       <c r="E11" s="30"/>
       <c r="F11" s="30"/>
@@ -29021,7 +29021,7 @@
       <c r="B12" s="35">
         <v>42</v>
       </c>
-      <c r="C12" s="65"/>
+      <c r="C12" s="66"/>
       <c r="D12" s="30"/>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
@@ -29034,7 +29034,7 @@
       <c r="B13" s="10">
         <v>81</v>
       </c>
-      <c r="C13" s="65" t="s">
+      <c r="C13" s="66" t="s">
         <v>1913</v>
       </c>
       <c r="D13" s="30"/>
@@ -29049,7 +29049,7 @@
       <c r="B14" s="10">
         <v>87</v>
       </c>
-      <c r="C14" s="65"/>
+      <c r="C14" s="66"/>
       <c r="D14" s="30"/>
       <c r="E14" s="30"/>
       <c r="F14" s="30"/>
@@ -33339,7 +33339,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="270">
+    <row r="126" spans="1:3" ht="285">
       <c r="A126" s="60">
         <v>19</v>
       </c>
@@ -33399,7 +33399,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="135">
+    <row r="132" spans="1:3" ht="120">
       <c r="A132" s="60">
         <v>24</v>
       </c>
